--- a/output/Tables/Best practice/cases_prev_target_area_sex.xlsx
+++ b/output/Tables/Best practice/cases_prev_target_area_sex.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="D2">
-        <v>497.8263307675485</v>
+        <v>8253.84642023883</v>
       </c>
       <c r="E2">
-        <v>531.0203463423876</v>
+        <v>7900.64771812378</v>
       </c>
       <c r="F2">
-        <v>473.7274910275815</v>
+        <v>8638.157298867451</v>
       </c>
       <c r="G2">
-        <v>1292.965093431151</v>
+        <v>121395.1226977583</v>
       </c>
       <c r="H2">
-        <v>1326.810213083224</v>
+        <v>109400.9630364136</v>
       </c>
       <c r="I2">
-        <v>1275.800095905312</v>
+        <v>132948.8626566701</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -475,13 +475,13 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>171964357.4263431</v>
+        <v>16145551318.80185</v>
       </c>
       <c r="N2">
-        <v>176465758.3400688</v>
+        <v>14550328083.84301</v>
       </c>
       <c r="O2">
-        <v>169681412.7554065</v>
+        <v>17682198733.33713</v>
       </c>
     </row>
     <row r="3">
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="D3">
-        <v>6103.339052972682</v>
+        <v>7159.110372896416</v>
       </c>
       <c r="E3">
-        <v>6503.078248760651</v>
+        <v>7398.725163138033</v>
       </c>
       <c r="F3">
-        <v>5814.098236759799</v>
+        <v>7018.726506230752</v>
       </c>
       <c r="G3">
-        <v>5030.429761841097</v>
+        <v>97970.7513926964</v>
       </c>
       <c r="H3">
-        <v>5128.634489951949</v>
+        <v>95805.3968277511</v>
       </c>
       <c r="I3">
-        <v>4992.643842842602</v>
+        <v>100772.5730761251</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>669047158.3248659</v>
+        <v>13030109935.22862</v>
       </c>
       <c r="N3">
-        <v>682108387.1636093</v>
+        <v>12742117778.0909</v>
       </c>
       <c r="O3">
-        <v>664021631.0980661</v>
+        <v>13402752219.12464</v>
       </c>
     </row>
     <row r="4">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="D4">
-        <v>2996.700526221636</v>
+        <v>9668.850608764476</v>
       </c>
       <c r="E4">
-        <v>2985.084868936879</v>
+        <v>8705.058033944282</v>
       </c>
       <c r="F4">
-        <v>3035.12270192156</v>
+        <v>10597.12059609972</v>
       </c>
       <c r="G4">
-        <v>9393.599296733659</v>
+        <v>142743.1400039292</v>
       </c>
       <c r="H4">
-        <v>8753.135953031933</v>
+        <v>117152.7275672453</v>
       </c>
       <c r="I4">
-        <v>10038.30832377661</v>
+        <v>166325.0909644189</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>1249348706.465577</v>
+        <v>18984837620.52258</v>
       </c>
       <c r="N4">
-        <v>1164167081.753247</v>
+        <v>15581312766.44362</v>
       </c>
       <c r="O4">
-        <v>1335095007.062289</v>
+        <v>22121237098.26771</v>
       </c>
     </row>
     <row r="5">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="D5">
-        <v>883.2804117969878</v>
+        <v>14843.60734043051</v>
       </c>
       <c r="E5">
-        <v>897.3846399769305</v>
+        <v>14016.41674585004</v>
       </c>
       <c r="F5">
-        <v>879.3721119864923</v>
+        <v>15701.38070724748</v>
       </c>
       <c r="G5">
-        <v>2401.650665886356</v>
+        <v>177126.4044864742</v>
       </c>
       <c r="H5">
-        <v>2412.485992118085</v>
+        <v>156721.249581694</v>
       </c>
       <c r="I5">
-        <v>2414.890035626931</v>
+        <v>196505.4098581946</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>319419538.5628853</v>
+        <v>23557811796.70107</v>
       </c>
       <c r="N5">
-        <v>320860636.9517053</v>
+        <v>20843926194.3653</v>
       </c>
       <c r="O5">
-        <v>321180374.7383817</v>
+        <v>26135219511.13988</v>
       </c>
     </row>
     <row r="6">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="D6">
-        <v>5434.16425193768</v>
+        <v>12211.01292613073</v>
       </c>
       <c r="E6">
-        <v>5722.106467291844</v>
+        <v>12427.53263445969</v>
       </c>
       <c r="F6">
-        <v>5235.593641071368</v>
+        <v>12138.26257153001</v>
       </c>
       <c r="G6">
-        <v>4943.273283604194</v>
+        <v>144929.8839420977</v>
       </c>
       <c r="H6">
-        <v>4924.072265542117</v>
+        <v>139878.7812818179</v>
       </c>
       <c r="I6">
-        <v>5006.516055904585</v>
+        <v>150677.8160579968</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>657455346.7193578</v>
+        <v>19275674564.29899</v>
       </c>
       <c r="N6">
-        <v>654901611.3171016</v>
+        <v>18603877910.48178</v>
       </c>
       <c r="O6">
-        <v>665866635.4353099</v>
+        <v>20040149535.71357</v>
       </c>
     </row>
     <row r="7">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="D7">
-        <v>3687.593684566508</v>
+        <v>15694.80586331956</v>
       </c>
       <c r="E7">
-        <v>3589.972979306652</v>
+        <v>13691.71794477737</v>
       </c>
       <c r="F7">
-        <v>3807.175929930162</v>
+        <v>17582.77858979543</v>
       </c>
       <c r="G7">
-        <v>10669.37765217196</v>
+        <v>213850.023146182</v>
       </c>
       <c r="H7">
-        <v>9901.899868080536</v>
+        <v>170561.9631321144</v>
       </c>
       <c r="I7">
-        <v>11436.39166977105</v>
+        <v>253486.24003958</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -740,19 +740,19 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>1419027227.738871</v>
+        <v>28442053078.44221</v>
       </c>
       <c r="N7">
-        <v>1316952682.454711</v>
+        <v>22684741096.57122</v>
       </c>
       <c r="O7">
-        <v>1521040092.07955</v>
+        <v>33713669925.26414</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -766,46 +766,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>16.19067133692936</v>
+        <v>4687.844341969944</v>
       </c>
       <c r="E8">
-        <v>3.528799106744248</v>
+        <v>3152.595720089405</v>
       </c>
       <c r="F8">
-        <v>32.65690897757692</v>
+        <v>6435.08892814103</v>
       </c>
       <c r="G8">
-        <v>5.593292428435344</v>
+        <v>5508.569800506694</v>
       </c>
       <c r="H8">
-        <v>0.9168272334042735</v>
+        <v>2769.21901644813</v>
       </c>
       <c r="I8">
-        <v>14.2733649552043</v>
+        <v>9430.01576510017</v>
       </c>
       <c r="J8">
-        <v>713798.1272312038</v>
+        <v>261122305.5364092</v>
       </c>
       <c r="K8">
-        <v>155574.1662190337</v>
+        <v>175605886.8004202</v>
       </c>
       <c r="L8">
-        <v>1439745.146094436</v>
+        <v>358447323.4753122</v>
       </c>
       <c r="M8">
-        <v>743907.8929819007</v>
+        <v>732639783.4673903</v>
       </c>
       <c r="N8">
-        <v>121938.0220427684</v>
+        <v>368306129.1876013</v>
       </c>
       <c r="O8">
-        <v>1898357.539042171</v>
+        <v>1254192096.758323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -819,46 +819,46 @@
         </is>
       </c>
       <c r="D9">
-        <v>69.96644975480149</v>
+        <v>3708.71240251773</v>
       </c>
       <c r="E9">
-        <v>15.24937047135656</v>
+        <v>2747.802670320614</v>
       </c>
       <c r="F9">
-        <v>141.1237331410189</v>
+        <v>4837.507922686886</v>
       </c>
       <c r="G9">
-        <v>13.37369720766987</v>
+        <v>4176.843557060938</v>
       </c>
       <c r="H9">
-        <v>2.192156045509016</v>
+        <v>2324.317228707781</v>
       </c>
       <c r="I9">
-        <v>34.12796013936774</v>
+        <v>6806.817169600731</v>
       </c>
       <c r="J9">
-        <v>3084610.870339935</v>
+        <v>206582698.2450425</v>
       </c>
       <c r="K9">
-        <v>672298.9959706978</v>
+        <v>153058104.3421988</v>
       </c>
       <c r="L9">
-        <v>6221722.022988104</v>
+        <v>269458866.3095054</v>
       </c>
       <c r="M9">
-        <v>1778701.728620093</v>
+        <v>555520193.0891048</v>
       </c>
       <c r="N9">
-        <v>291556.7540526991</v>
+        <v>309134191.4181349</v>
       </c>
       <c r="O9">
-        <v>4539018.698535909</v>
+        <v>905306683.5568973</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -872,46 +872,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>132.2343368561681</v>
+        <v>5805.284719255748</v>
       </c>
       <c r="E10">
-        <v>28.60199494038688</v>
+        <v>3593.038412385754</v>
       </c>
       <c r="F10">
-        <v>266.7869477047978</v>
+        <v>8251.413091497043</v>
       </c>
       <c r="G10">
-        <v>48.95439033087773</v>
+        <v>7002.395128658082</v>
       </c>
       <c r="H10">
-        <v>7.939950644517312</v>
+        <v>3189.989338027079</v>
       </c>
       <c r="I10">
-        <v>124.9692279514181</v>
+        <v>12421.74868401434</v>
       </c>
       <c r="J10">
-        <v>5829815.208977875</v>
+        <v>323365969.4319832</v>
       </c>
       <c r="K10">
-        <v>1260976.15093683</v>
+        <v>200139425.6467111</v>
       </c>
       <c r="L10">
-        <v>11761836.16346142</v>
+        <v>459620212.0225677</v>
       </c>
       <c r="M10">
-        <v>6510933.914006738</v>
+        <v>931318552.1115249</v>
       </c>
       <c r="N10">
-        <v>1056013.435720803</v>
+        <v>424268581.9576015</v>
       </c>
       <c r="O10">
-        <v>16620907.3175386</v>
+        <v>1652092574.973907</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -925,46 +925,46 @@
         </is>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>7008.923814313164</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>4627.531230201515</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>9706.405273327398</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>6625.168089974998</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3257.10515275798</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>11453.87714641847</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>390411074.3048729</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>257762744.5846848</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>540666186.5348845</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>881147355.9666748</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>433194985.3168113</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1523365660.473656</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -978,46 +978,46 @@
         </is>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>5382.043341801748</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>3926.35873289981</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>7082.764038007527</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>4998.730831565939</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2734.963744078354</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>8219.536670523205</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>299790578.2250413</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>218706034.1399854</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>394524122.4450952</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>664831200.5982699</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>363750177.9624211</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1093198377.179586</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1031,46 +1031,46 @@
         </is>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>8155.128332356485</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>4887.340278464571</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>11733.58196480755</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>8752.030267437309</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>3869.556380109978</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>15673.83342815437</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>454256958.3689213</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>272234628.191034</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>653583982.6037109</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1164020025.569162</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>514650998.5546271</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2084619845.944531</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1084,46 +1084,46 @@
         </is>
       </c>
       <c r="D14">
-        <v>229.3264735633352</v>
+        <v>4864.771220900318</v>
       </c>
       <c r="E14">
-        <v>179.139135958496</v>
+        <v>1060.289594025195</v>
       </c>
       <c r="F14">
-        <v>289.5284093870751</v>
+        <v>9812.341171753254</v>
       </c>
       <c r="G14">
-        <v>48.83405328502028</v>
+        <v>9118.384506381004</v>
       </c>
       <c r="H14">
-        <v>28.81989144409306</v>
+        <v>1572.32775637972</v>
       </c>
       <c r="I14">
-        <v>76.93922901088308</v>
+        <v>21237.37608941478</v>
       </c>
       <c r="J14">
-        <v>12773943.2304249</v>
+        <v>72032667.46787091</v>
       </c>
       <c r="K14">
-        <v>9978408.151160141</v>
+        <v>15699708.01873104</v>
       </c>
       <c r="L14">
-        <v>16127311.45967885</v>
+        <v>145291335.7301504</v>
       </c>
       <c r="M14">
-        <v>6494929.086907698</v>
+        <v>1212745139.348674</v>
       </c>
       <c r="N14">
-        <v>3833045.562064377</v>
+        <v>209119591.5985027</v>
       </c>
       <c r="O14">
-        <v>10232917.45844745</v>
+        <v>2824571019.892166</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1137,46 +1137,46 @@
         </is>
       </c>
       <c r="D15">
-        <v>2107.381285822162</v>
+        <v>3559.942352286718</v>
       </c>
       <c r="E15">
-        <v>1639.24676076469</v>
+        <v>775.898733992386</v>
       </c>
       <c r="F15">
-        <v>2669.027535794156</v>
+        <v>7180.475160339917</v>
       </c>
       <c r="G15">
-        <v>205.2871031946251</v>
+        <v>6708.180819770454</v>
       </c>
       <c r="H15">
-        <v>119.3207940332402</v>
+        <v>1156.724515220647</v>
       </c>
       <c r="I15">
-        <v>326.4888377413678</v>
+        <v>15623.83762667257</v>
       </c>
       <c r="J15">
-        <v>117385352.382866</v>
+        <v>52712066.41030943</v>
       </c>
       <c r="K15">
-        <v>91309323.06811467</v>
+        <v>11488732.55422525</v>
       </c>
       <c r="L15">
-        <v>148670171.7988065</v>
+        <v>106321295.6991528</v>
       </c>
       <c r="M15">
-        <v>27303184.72488514</v>
+        <v>892188049.0294704</v>
       </c>
       <c r="N15">
-        <v>15869665.60642094</v>
+        <v>153844360.5243461</v>
       </c>
       <c r="O15">
-        <v>43423015.41960192</v>
+        <v>2077970404.347451</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1190,46 +1190,46 @@
         </is>
       </c>
       <c r="D16">
-        <v>1627.366805051451</v>
+        <v>7192.012576144401</v>
       </c>
       <c r="E16">
-        <v>1146.617008553357</v>
+        <v>1386.536862302079</v>
       </c>
       <c r="F16">
-        <v>2179.03706332675</v>
+        <v>14562.37346730163</v>
       </c>
       <c r="G16">
-        <v>385.4997354692616</v>
+        <v>14438.30653172097</v>
       </c>
       <c r="H16">
-        <v>201.6924739162426</v>
+        <v>2114.134885455231</v>
       </c>
       <c r="I16">
-        <v>646.8831945144289</v>
+        <v>33797.27124008795</v>
       </c>
       <c r="J16">
-        <v>90647585.7749757</v>
+        <v>106492130.2149702</v>
       </c>
       <c r="K16">
-        <v>63868860.61043941</v>
+        <v>20530451.3201069</v>
       </c>
       <c r="L16">
-        <v>121376722.5014262</v>
+        <v>215625063.9303355</v>
       </c>
       <c r="M16">
-        <v>51271464.8174118</v>
+        <v>1920294768.71889</v>
       </c>
       <c r="N16">
-        <v>26825099.03086026</v>
+        <v>281179939.7655457</v>
       </c>
       <c r="O16">
-        <v>86035464.87041904</v>
+        <v>4495037074.931697</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1243,46 +1243,46 @@
         </is>
       </c>
       <c r="D17">
-        <v>443.2255722811445</v>
+        <v>2943.198685913449</v>
       </c>
       <c r="E17">
-        <v>324.4843305833305</v>
+        <v>641.4778410165663</v>
       </c>
       <c r="F17">
-        <v>582.0094095954435</v>
+        <v>5936.490809344574</v>
       </c>
       <c r="G17">
-        <v>80.97669426675637</v>
+        <v>3370.588964715729</v>
       </c>
       <c r="H17">
-        <v>46.33835012398283</v>
+        <v>581.2071843275567</v>
       </c>
       <c r="I17">
-        <v>129.9183396608188</v>
+        <v>7850.345139142364</v>
       </c>
       <c r="J17">
-        <v>24688550.82720436</v>
+        <v>43579942.94232056</v>
       </c>
       <c r="K17">
-        <v>18074426.18215264</v>
+        <v>9498362.391932283</v>
       </c>
       <c r="L17">
-        <v>32419088.13328537</v>
+        <v>87901619.41396514</v>
       </c>
       <c r="M17">
-        <v>10769900.3374786</v>
+        <v>448288332.307192</v>
       </c>
       <c r="N17">
-        <v>6163000.566489717</v>
+        <v>77300555.51556504</v>
       </c>
       <c r="O17">
-        <v>17279139.17488889</v>
+        <v>1044095903.505934</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1296,46 +1296,46 @@
         </is>
       </c>
       <c r="D18">
-        <v>1787.552580800044</v>
+        <v>2165.33972017152</v>
       </c>
       <c r="E18">
-        <v>1363.676871819488</v>
+        <v>471.941447721844</v>
       </c>
       <c r="F18">
-        <v>2291.392899290456</v>
+        <v>4367.533666493687</v>
       </c>
       <c r="G18">
-        <v>175.2340898396513</v>
+        <v>2461.075219908059</v>
       </c>
       <c r="H18">
-        <v>99.44282706640625</v>
+        <v>424.3752691161218</v>
       </c>
       <c r="I18">
-        <v>282.5065183172316</v>
+        <v>5732.021937981513</v>
       </c>
       <c r="J18">
-        <v>99570253.85572389</v>
+        <v>32062185.23657968</v>
       </c>
       <c r="K18">
-        <v>75959529.11408907</v>
+        <v>6988037.01641736</v>
       </c>
       <c r="L18">
-        <v>127635167.276277</v>
+        <v>64670070.99977201</v>
       </c>
       <c r="M18">
-        <v>23306133.94867362</v>
+        <v>327323004.2477719</v>
       </c>
       <c r="N18">
-        <v>13225895.99983203</v>
+        <v>56441910.79244421</v>
       </c>
       <c r="O18">
-        <v>37573366.9361918</v>
+        <v>762358917.7515413</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1349,46 +1349,46 @@
         </is>
       </c>
       <c r="D19">
-        <v>1793.570554379592</v>
+        <v>3977.939897297059</v>
       </c>
       <c r="E19">
-        <v>1233.838143283853</v>
+        <v>802.3522507055084</v>
       </c>
       <c r="F19">
-        <v>2431.356826984171</v>
+        <v>8043.567431528649</v>
       </c>
       <c r="G19">
-        <v>368.3756440087397</v>
+        <v>5240.304728400624</v>
       </c>
       <c r="H19">
-        <v>191.8771122443416</v>
+        <v>791.3809991924962</v>
       </c>
       <c r="I19">
-        <v>619.3572273320652</v>
+        <v>12255.6781953113</v>
       </c>
       <c r="J19">
-        <v>99905467.02005218</v>
+        <v>58901356.0592775</v>
       </c>
       <c r="K19">
-        <v>68727252.2571971</v>
+        <v>11880429.77619646</v>
       </c>
       <c r="L19">
-        <v>135431437.9766723</v>
+        <v>119101102.9586445</v>
       </c>
       <c r="M19">
-        <v>48993960.65316238</v>
+        <v>696960528.877283</v>
       </c>
       <c r="N19">
-        <v>25519655.92849743</v>
+        <v>105253672.892602</v>
       </c>
       <c r="O19">
-        <v>82374511.23516467</v>
+        <v>1630005199.976403</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1402,46 +1402,46 @@
         </is>
       </c>
       <c r="D20">
-        <v>291.5369830769008</v>
+        <v>758.7457610219977</v>
       </c>
       <c r="E20">
-        <v>63.54124693508795</v>
+        <v>-60.16649273703359</v>
       </c>
       <c r="F20">
-        <v>588.0359450088987</v>
+        <v>1529.149155900641</v>
       </c>
       <c r="G20">
-        <v>97.39044695134848</v>
+        <v>1632.108725067148</v>
       </c>
       <c r="H20">
-        <v>16.79351236402363</v>
+        <v>-96.31436630534563</v>
       </c>
       <c r="I20">
-        <v>226.8293849611831</v>
+        <v>4176.140162739625</v>
       </c>
       <c r="J20">
-        <v>4316788.108419673</v>
+        <v>57058439.97461542</v>
       </c>
       <c r="K20">
-        <v>940855.2433678483</v>
+        <v>-4524580.420317656</v>
       </c>
       <c r="L20">
-        <v>8707048.237746747</v>
+        <v>114993545.6728838</v>
       </c>
       <c r="M20">
-        <v>12952929.44452935</v>
+        <v>217070460.4339306</v>
       </c>
       <c r="N20">
-        <v>2233537.144415143</v>
+        <v>-12809810.71861097</v>
       </c>
       <c r="O20">
-        <v>30168308.19983735</v>
+        <v>555426641.6443702</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1455,46 +1455,46 @@
         </is>
       </c>
       <c r="D21">
-        <v>875.3169477309697</v>
+        <v>543.8805687008911</v>
       </c>
       <c r="E21">
-        <v>190.7776150224133</v>
+        <v>-43.12826241359065</v>
       </c>
       <c r="F21">
-        <v>1765.531848168689</v>
+        <v>1096.117507687289</v>
       </c>
       <c r="G21">
-        <v>191.3669027157217</v>
+        <v>1175.397060655109</v>
       </c>
       <c r="H21">
-        <v>32.99833348569358</v>
+        <v>-69.36279508554547</v>
       </c>
       <c r="I21">
-        <v>445.7073378728611</v>
+        <v>3007.534238851616</v>
       </c>
       <c r="J21">
-        <v>12960818.04505245</v>
+        <v>40900362.6468757</v>
       </c>
       <c r="K21">
-        <v>2824844.145636877</v>
+        <v>-3243288.46176442</v>
       </c>
       <c r="L21">
-        <v>26142230.07583378</v>
+        <v>82429132.69559166</v>
       </c>
       <c r="M21">
-        <v>25451798.06119099</v>
+        <v>156327809.0671294</v>
       </c>
       <c r="N21">
-        <v>4388778.353597246</v>
+        <v>-9225251.746377548</v>
       </c>
       <c r="O21">
-        <v>59279075.93709052</v>
+        <v>400002053.7672649</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1508,46 +1508,46 @@
         </is>
       </c>
       <c r="D22">
-        <v>2680.709336596636</v>
+        <v>1067.675666851944</v>
       </c>
       <c r="E22">
-        <v>578.0707210095752</v>
+        <v>-80.04343457346833</v>
       </c>
       <c r="F22">
-        <v>5408.959930201819</v>
+        <v>2137.130433342855</v>
       </c>
       <c r="G22">
-        <v>988.2850533113897</v>
+        <v>2455.370387430866</v>
       </c>
       <c r="H22">
-        <v>168.2887626266392</v>
+        <v>-133.9002434626026</v>
       </c>
       <c r="I22">
-        <v>2302.746394598881</v>
+        <v>6223.267918041822</v>
       </c>
       <c r="J22">
-        <v>39693263.14698636</v>
+        <v>80290277.82293293</v>
       </c>
       <c r="K22">
-        <v>8559493.165988779</v>
+        <v>-6019346.323359375</v>
       </c>
       <c r="L22">
-        <v>80090469.68649833</v>
+        <v>160714345.7178162</v>
       </c>
       <c r="M22">
-        <v>131441912.0904148</v>
+        <v>326564261.5283052</v>
       </c>
       <c r="N22">
-        <v>22382405.42934301</v>
+        <v>-17808732.38052614</v>
       </c>
       <c r="O22">
-        <v>306265270.4816512</v>
+        <v>827694633.0995623</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1561,46 +1561,46 @@
         </is>
       </c>
       <c r="D23">
-        <v>184.1777044578762</v>
+        <v>1082.033409135065</v>
       </c>
       <c r="E23">
-        <v>40.14201174541381</v>
+        <v>-85.80233142161192</v>
       </c>
       <c r="F23">
-        <v>371.4901257034986</v>
+        <v>2180.691556031257</v>
       </c>
       <c r="G23">
-        <v>35.70330428983102</v>
+        <v>2038.868515051613</v>
       </c>
       <c r="H23">
-        <v>6.156495845298799</v>
+        <v>-120.318166302945</v>
       </c>
       <c r="I23">
-        <v>83.15557435720551</v>
+        <v>5216.932279987687</v>
       </c>
       <c r="J23">
-        <v>2727119.269907773</v>
+        <v>81369994.40036626</v>
       </c>
       <c r="K23">
-        <v>594382.7679143419</v>
+        <v>-6452421.125236639</v>
       </c>
       <c r="L23">
-        <v>5500654.291291706</v>
+        <v>163990185.7051065</v>
       </c>
       <c r="M23">
-        <v>4748539.470547526</v>
+        <v>271169512.5018645</v>
       </c>
       <c r="N23">
-        <v>818813.9474247403</v>
+        <v>-16002316.11829169</v>
       </c>
       <c r="O23">
-        <v>11059691.38950833</v>
+        <v>693851993.2383624</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1614,46 +1614,46 @@
         </is>
       </c>
       <c r="D24">
-        <v>555.3103215909572</v>
+        <v>786.6290410376989</v>
       </c>
       <c r="E24">
-        <v>121.0313350210752</v>
+        <v>-62.37756164935282</v>
       </c>
       <c r="F24">
-        <v>1120.072061813848</v>
+        <v>1585.34412434741</v>
       </c>
       <c r="G24">
-        <v>74.52729466285091</v>
+        <v>1494.340577476141</v>
       </c>
       <c r="H24">
-        <v>12.85110689555657</v>
+        <v>-88.18436146651824</v>
       </c>
       <c r="I24">
-        <v>173.579451993277</v>
+        <v>3823.627437659141</v>
       </c>
       <c r="J24">
-        <v>8222479.931797295</v>
+        <v>59155290.51507618</v>
       </c>
       <c r="K24">
-        <v>1792110.977657063</v>
+        <v>-4690855.013592984</v>
       </c>
       <c r="L24">
-        <v>16584907.01927763</v>
+        <v>119219463.4950496</v>
       </c>
       <c r="M24">
-        <v>9912130.19015917</v>
+        <v>198747296.8043267</v>
       </c>
       <c r="N24">
-        <v>1709197.217109024</v>
+        <v>-11728520.07504693</v>
       </c>
       <c r="O24">
-        <v>23086067.11510585</v>
+        <v>508542449.2086657</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1667,46 +1667,46 @@
         </is>
       </c>
       <c r="D25">
-        <v>904.9477199011062</v>
+        <v>1644.116453384767</v>
       </c>
       <c r="E25">
-        <v>196.1300409851613</v>
+        <v>-120.8564014989858</v>
       </c>
       <c r="F25">
-        <v>1825.639466415742</v>
+        <v>3283.36722572006</v>
       </c>
       <c r="G25">
-        <v>221.5939707322441</v>
+        <v>3398.746929158277</v>
       </c>
       <c r="H25">
-        <v>37.90229542337522</v>
+        <v>-181.0793428443642</v>
       </c>
       <c r="I25">
-        <v>516.247417153607</v>
+        <v>8591.265653892089</v>
       </c>
       <c r="J25">
-        <v>13399560.88857569</v>
+        <v>123639201.4109879</v>
       </c>
       <c r="K25">
-        <v>2904097.516867276</v>
+        <v>-9088522.249125211</v>
       </c>
       <c r="L25">
-        <v>27032243.57921787</v>
+        <v>246912498.7413736</v>
       </c>
       <c r="M25">
-        <v>29471998.10738847</v>
+        <v>452033341.5780509</v>
       </c>
       <c r="N25">
-        <v>5041005.291308904</v>
+        <v>-24083552.59830045</v>
       </c>
       <c r="O25">
-        <v>68660906.48142973</v>
+        <v>1142638331.967648</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1720,46 +1720,46 @@
         </is>
       </c>
       <c r="D26">
-        <v>43.21603712294542</v>
+        <v>1751.429393137576</v>
       </c>
       <c r="E26">
-        <v>-3.426915203030243</v>
+        <v>1452.226991656893</v>
       </c>
       <c r="F26">
-        <v>87.09606047605546</v>
+        <v>2039.358846460138</v>
       </c>
       <c r="G26">
-        <v>16.81766880787904</v>
+        <v>3916.057058909889</v>
       </c>
       <c r="H26">
-        <v>-0.992448045333123</v>
+        <v>2484.655924856676</v>
       </c>
       <c r="I26">
-        <v>43.0320241988459</v>
+        <v>5345.155598953805</v>
       </c>
       <c r="J26">
-        <v>3249889.207682615</v>
+        <v>29492319.55104359</v>
       </c>
       <c r="K26">
-        <v>-257707.4501830772</v>
+        <v>24454050.31251043</v>
       </c>
       <c r="L26">
-        <v>6549710.843859845</v>
+        <v>34340763.61554222</v>
       </c>
       <c r="M26">
-        <v>2236749.951447912</v>
+        <v>520835588.8350153</v>
       </c>
       <c r="N26">
-        <v>-131995.5900293054</v>
+        <v>330459238.0059379</v>
       </c>
       <c r="O26">
-        <v>5723259.218446505</v>
+        <v>710905694.660856</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1773,46 +1773,46 @@
         </is>
       </c>
       <c r="D27">
-        <v>124.1738039694135</v>
+        <v>1443.781464982335</v>
       </c>
       <c r="E27">
-        <v>-9.846647794898015</v>
+        <v>1290.110710163457</v>
       </c>
       <c r="F27">
-        <v>250.2554574658041</v>
+        <v>1597.570145249</v>
       </c>
       <c r="G27">
-        <v>37.78960541262339</v>
+        <v>3062.181862612254</v>
       </c>
       <c r="H27">
-        <v>-2.23004867405271</v>
+        <v>2095.516575980358</v>
       </c>
       <c r="I27">
-        <v>96.69373521132691</v>
+        <v>3985.027869796784</v>
       </c>
       <c r="J27">
-        <v>9337994.232303867</v>
+        <v>24311836.08883753</v>
       </c>
       <c r="K27">
-        <v>-740477.7608241254</v>
+        <v>21724174.24844243</v>
       </c>
       <c r="L27">
-        <v>18819460.65688593</v>
+        <v>26901483.67584785</v>
       </c>
       <c r="M27">
-        <v>5026017.519878911</v>
+        <v>407270187.7274298</v>
       </c>
       <c r="N27">
-        <v>-296596.4736490105</v>
+        <v>278703704.6053876</v>
       </c>
       <c r="O27">
-        <v>12860266.78310648</v>
+        <v>530008706.6829723</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1826,46 +1826,46 @@
         </is>
       </c>
       <c r="D28">
-        <v>375.0145143396441</v>
+        <v>2166.271502732026</v>
       </c>
       <c r="E28">
-        <v>-29.57933756887368</v>
+        <v>1698.570538874215</v>
       </c>
       <c r="F28">
-        <v>755.2898018080193</v>
+        <v>2609.96162781205</v>
       </c>
       <c r="G28">
-        <v>158.0046810903636</v>
+        <v>4879.810044502176</v>
       </c>
       <c r="H28">
-        <v>-9.262247804694383</v>
+        <v>2882.091888233809</v>
       </c>
       <c r="I28">
-        <v>403.958136000019</v>
+        <v>6932.6862861466</v>
       </c>
       <c r="J28">
-        <v>28201466.49285558</v>
+        <v>36477845.8345046</v>
       </c>
       <c r="K28">
-        <v>-2224395.764516867</v>
+        <v>28602229.30410286</v>
       </c>
       <c r="L28">
-        <v>56798548.38576464</v>
+        <v>43949143.85072712</v>
       </c>
       <c r="M28">
-        <v>21014622.58501836</v>
+        <v>649014735.9187895</v>
       </c>
       <c r="N28">
-        <v>-1231878.958024353</v>
+        <v>383318221.1350965</v>
       </c>
       <c r="O28">
-        <v>53726432.08800253</v>
+        <v>922047276.0574977</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1879,46 +1879,46 @@
         </is>
       </c>
       <c r="D29">
-        <v>70.36001268441012</v>
+        <v>1404.784553633325</v>
       </c>
       <c r="E29">
-        <v>-5.579359265812622</v>
+        <v>1156.777763122008</v>
       </c>
       <c r="F29">
-        <v>141.801061083496</v>
+        <v>1642.93046329017</v>
       </c>
       <c r="G29">
-        <v>20.46428115752175</v>
+        <v>1991.198639260032</v>
       </c>
       <c r="H29">
-        <v>-1.207642751557517</v>
+        <v>1226.755749223694</v>
       </c>
       <c r="I29">
-        <v>52.3627532473403</v>
+        <v>2764.540690032691</v>
       </c>
       <c r="J29">
-        <v>5291143.313880314</v>
+        <v>23655167.09863161</v>
       </c>
       <c r="K29">
-        <v>-419573.3961483747</v>
+        <v>19478980.75321149</v>
       </c>
       <c r="L29">
-        <v>10663581.59453999</v>
+        <v>27665306.07134325</v>
       </c>
       <c r="M29">
-        <v>2721749.393950393</v>
+        <v>264829419.0215843</v>
       </c>
       <c r="N29">
-        <v>-160616.4859571497</v>
+        <v>163158514.6467513</v>
       </c>
       <c r="O29">
-        <v>6964246.18189626</v>
+        <v>367683911.7743478</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1932,46 +1932,46 @@
         </is>
       </c>
       <c r="D30">
-        <v>148.1961149408115</v>
+        <v>1095.455908257531</v>
       </c>
       <c r="E30">
-        <v>-11.7515522738905</v>
+        <v>971.2334641020432</v>
       </c>
       <c r="F30">
-        <v>298.6691665522541</v>
+        <v>1218.999635328685</v>
       </c>
       <c r="G30">
-        <v>40.88771395476844</v>
+        <v>1545.029911519845</v>
       </c>
       <c r="H30">
-        <v>-2.412874950512688</v>
+        <v>1036.118178793872</v>
       </c>
       <c r="I30">
-        <v>104.6209862042694</v>
+        <v>2037.693206988772</v>
       </c>
       <c r="J30">
-        <v>11144496.03966396</v>
+        <v>18446382.03914857</v>
       </c>
       <c r="K30">
-        <v>-883728.4825488374</v>
+        <v>16354600.30201432</v>
       </c>
       <c r="L30">
-        <v>22460219.99389603</v>
+        <v>20526734.85929978</v>
       </c>
       <c r="M30">
-        <v>5438065.955984202</v>
+        <v>205488978.2321393</v>
       </c>
       <c r="N30">
-        <v>-320912.3684181874</v>
+        <v>137803717.7795849</v>
       </c>
       <c r="O30">
-        <v>13914591.16516783</v>
+        <v>271013196.5295067</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1985,46 +1985,46 @@
         </is>
       </c>
       <c r="D31">
-        <v>399.6386456338798</v>
+        <v>1482.203267110881</v>
       </c>
       <c r="E31">
-        <v>-31.52963306932394</v>
+        <v>1146.621587111518</v>
       </c>
       <c r="F31">
-        <v>804.9090174660442</v>
+        <v>1799.728459276041</v>
       </c>
       <c r="G31">
-        <v>145.0163561529458</v>
+        <v>2366.292157278386</v>
       </c>
       <c r="H31">
-        <v>-8.50512374825249</v>
+        <v>1347.385759074039</v>
       </c>
       <c r="I31">
-        <v>370.7748727386236</v>
+        <v>3425.472626599474</v>
       </c>
       <c r="J31">
-        <v>30053225.79031343</v>
+        <v>24958820.8148801</v>
       </c>
       <c r="K31">
-        <v>-2371059.936446225</v>
+        <v>19307960.90537084</v>
       </c>
       <c r="L31">
-        <v>60529963.02246395</v>
+        <v>30305627.52574926</v>
       </c>
       <c r="M31">
-        <v>19287175.3683418</v>
+        <v>314716856.9180253</v>
       </c>
       <c r="N31">
-        <v>-1131181.458517581</v>
+        <v>179202305.9568473</v>
       </c>
       <c r="O31">
-        <v>49313058.07423694</v>
+        <v>455587859.33773</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2038,46 +2038,46 @@
         </is>
       </c>
       <c r="D32">
-        <v>82.78538330732383</v>
+        <v>27229.71362371212</v>
       </c>
       <c r="E32">
-        <v>77.51448258017231</v>
+        <v>19342.0557325939</v>
       </c>
       <c r="F32">
-        <v>88.41825698692605</v>
+        <v>33626.07852962624</v>
       </c>
       <c r="G32">
-        <v>28.43672948039629</v>
+        <v>84301.80071209511</v>
       </c>
       <c r="H32">
-        <v>20.57991572493152</v>
+        <v>37042.89974154739</v>
       </c>
       <c r="I32">
-        <v>35.57557789945198</v>
+        <v>159079.0458373938</v>
       </c>
       <c r="J32">
-        <v>1394023.069512026</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>1305266.37216752</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>1488875.029402849</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>3782085.020892706</v>
+        <v>11212139494.70865</v>
       </c>
       <c r="N32">
-        <v>2737128.791415892</v>
+        <v>4926705665.625802</v>
       </c>
       <c r="O32">
-        <v>4731551.860627113</v>
+        <v>21157513096.37338</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2091,46 +2091,46 @@
         </is>
       </c>
       <c r="D33">
-        <v>1279.051995957285</v>
+        <v>20097.78915929206</v>
       </c>
       <c r="E33">
-        <v>1168.656886772535</v>
+        <v>14276.04283294534</v>
       </c>
       <c r="F33">
-        <v>1392.149605714219</v>
+        <v>24818.83746121083</v>
       </c>
       <c r="G33">
-        <v>214.049335547024</v>
+        <v>62224.14202283687</v>
       </c>
       <c r="H33">
-        <v>151.7616108071057</v>
+        <v>27341.79620109869</v>
       </c>
       <c r="I33">
-        <v>271.810866305908</v>
+        <v>117418.0985154587</v>
       </c>
       <c r="J33">
-        <v>21537956.55992471</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>19679013.31636271</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>23442407.2106217</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>28468561.62775419</v>
+        <v>8275810889.037303</v>
       </c>
       <c r="N33">
-        <v>20184294.23734505</v>
+        <v>3636458894.746126</v>
       </c>
       <c r="O33">
-        <v>36150845.21868577</v>
+        <v>15616607102.556</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2144,46 +2144,46 @@
         </is>
       </c>
       <c r="D34">
-        <v>513.5534759229826</v>
+        <v>41432.09422520552</v>
       </c>
       <c r="E34">
-        <v>450.1499044184512</v>
+        <v>29598.55131878856</v>
       </c>
       <c r="F34">
-        <v>576.0932120700583</v>
+        <v>51113.88206723896</v>
       </c>
       <c r="G34">
-        <v>214.693935080397</v>
+        <v>137230.2558237958</v>
       </c>
       <c r="H34">
-        <v>140.9961924261269</v>
+        <v>60723.0700272856</v>
       </c>
       <c r="I34">
-        <v>286.9359076876938</v>
+        <v>258640.5018472947</v>
       </c>
       <c r="J34">
-        <v>8647726.981067097</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>7580074.240502289</v>
+        <v>0</v>
       </c>
       <c r="L34">
-        <v>9700833.598047726</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>28554293.3656928</v>
+        <v>18251624024.56485</v>
       </c>
       <c r="N34">
-        <v>18752493.59267487</v>
+        <v>8076168313.628985</v>
       </c>
       <c r="O34">
-        <v>38162475.72246328</v>
+        <v>34399186745.69019</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2197,46 +2197,46 @@
         </is>
       </c>
       <c r="D35">
-        <v>65.04026393381929</v>
+        <v>14364.40871190271</v>
       </c>
       <c r="E35">
-        <v>56.45239109492766</v>
+        <v>10203.45633122762</v>
       </c>
       <c r="F35">
-        <v>73.46468054076773</v>
+        <v>17738.66380135072</v>
       </c>
       <c r="G35">
-        <v>24.8939195376865</v>
+        <v>37836.07740130918</v>
       </c>
       <c r="H35">
-        <v>16.8891237352076</v>
+        <v>16625.48142449141</v>
       </c>
       <c r="I35">
-        <v>32.58265414556453</v>
+        <v>71397.37277719221</v>
       </c>
       <c r="J35">
-        <v>1095213.004381584</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>950601.8136474865</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>1237071.755625988</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>3310891.298512305</v>
+        <v>5032198294.374121</v>
       </c>
       <c r="N35">
-        <v>2246253.456782611</v>
+        <v>2211189029.457358</v>
       </c>
       <c r="O35">
-        <v>4333493.001360083</v>
+        <v>9495850579.366564</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2250,46 +2250,46 @@
         </is>
       </c>
       <c r="D36">
-        <v>584.8207833615201</v>
+        <v>10566.24417500289</v>
       </c>
       <c r="E36">
-        <v>531.5937974928411</v>
+        <v>7505.509846388188</v>
       </c>
       <c r="F36">
-        <v>639.0062120542417</v>
+        <v>13048.29574419216</v>
       </c>
       <c r="G36">
-        <v>58.07996611466014</v>
+        <v>27657.20615718402</v>
       </c>
       <c r="H36">
-        <v>39.89230617187984</v>
+        <v>12152.80226706807</v>
       </c>
       <c r="I36">
-        <v>75.39562929015835</v>
+        <v>52189.65584185514</v>
       </c>
       <c r="J36">
-        <v>9847797.171024626</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>8951507.955981961</v>
+        <v>0</v>
       </c>
       <c r="L36">
-        <v>10760225.60478136</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>7724635.493249798</v>
+        <v>3678408418.905475</v>
       </c>
       <c r="N36">
-        <v>5305676.720860018</v>
+        <v>1616322701.520054</v>
       </c>
       <c r="O36">
-        <v>10027618.69559106</v>
+        <v>6941224226.966733</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2303,358 +2303,40 @@
         </is>
       </c>
       <c r="D37">
-        <v>249.9046285231187</v>
+        <v>22668.93349040181</v>
       </c>
       <c r="E37">
-        <v>212.2861368690382</v>
+        <v>16203.53610441969</v>
       </c>
       <c r="F37">
-        <v>286.4157088505945</v>
+        <v>27963.41374996311</v>
       </c>
       <c r="G37">
-        <v>89.17417522775236</v>
+        <v>65562.36040230785</v>
       </c>
       <c r="H37">
-        <v>57.45337750243028</v>
+        <v>29027.91250159551</v>
       </c>
       <c r="I37">
-        <v>120.5950022279204</v>
+        <v>123553.8129125457</v>
       </c>
       <c r="J37">
-        <v>4208144.039700803</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>3574686.258737743</v>
+        <v>0</v>
       </c>
       <c r="L37">
-        <v>4822954.121335156</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>11860165.30529106</v>
+        <v>8719793933.506945</v>
       </c>
       <c r="N37">
-        <v>7641299.207823227</v>
+        <v>3860712362.712203</v>
       </c>
       <c r="O37">
-        <v>16039135.29631341</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>1611.773857194375</v>
-      </c>
-      <c r="E38">
-        <v>1144.889740854406</v>
-      </c>
-      <c r="F38">
-        <v>1990.385761781217</v>
-      </c>
-      <c r="G38">
-        <v>1736.236687266722</v>
-      </c>
-      <c r="H38">
-        <v>762.9165805563837</v>
-      </c>
-      <c r="I38">
-        <v>3276.310508497123</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>230919479.4064741</v>
-      </c>
-      <c r="N38">
-        <v>101467905.213999</v>
-      </c>
-      <c r="O38">
-        <v>435749297.6301174</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>4907.043917173984</v>
-      </c>
-      <c r="E39">
-        <v>3485.615685859222</v>
-      </c>
-      <c r="F39">
-        <v>6059.727486943845</v>
-      </c>
-      <c r="G39">
-        <v>3478.799664263336</v>
-      </c>
-      <c r="H39">
-        <v>1528.61298448808</v>
-      </c>
-      <c r="I39">
-        <v>6564.558841873678</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>462680355.3470237</v>
-      </c>
-      <c r="N39">
-        <v>203305526.9369146</v>
-      </c>
-      <c r="O39">
-        <v>873086325.9691992</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>16366.76429439732</v>
-      </c>
-      <c r="E40">
-        <v>11631.37085156342</v>
-      </c>
-      <c r="F40">
-        <v>20209.6944666328</v>
-      </c>
-      <c r="G40">
-        <v>19926.47994449874</v>
-      </c>
-      <c r="H40">
-        <v>8760.465379891446</v>
-      </c>
-      <c r="I40">
-        <v>37598.19676128398</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>2650221832.618332</v>
-      </c>
-      <c r="N40">
-        <v>1165141895.525562</v>
-      </c>
-      <c r="O40">
-        <v>5000560169.25077</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>831.6476745121881</v>
-      </c>
-      <c r="E41">
-        <v>590.7434757701255</v>
-      </c>
-      <c r="F41">
-        <v>1027.004925522808</v>
-      </c>
-      <c r="G41">
-        <v>656.9967491187444</v>
-      </c>
-      <c r="H41">
-        <v>288.6897373787222</v>
-      </c>
-      <c r="I41">
-        <v>1239.764928924988</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>87380567.63279301</v>
-      </c>
-      <c r="N41">
-        <v>38395735.07137005</v>
-      </c>
-      <c r="O41">
-        <v>164888735.5470234</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>2028.499112134994</v>
-      </c>
-      <c r="E42">
-        <v>1440.901781877923</v>
-      </c>
-      <c r="F42">
-        <v>2505.001388722999</v>
-      </c>
-      <c r="G42">
-        <v>1379.633869593402</v>
-      </c>
-      <c r="H42">
-        <v>606.2223900284836</v>
-      </c>
-      <c r="I42">
-        <v>2603.394443843484</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>183491304.6559225</v>
-      </c>
-      <c r="N42">
-        <v>80627577.87378831</v>
-      </c>
-      <c r="O42">
-        <v>346251461.0311834</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>6128.781285981382</v>
-      </c>
-      <c r="E43">
-        <v>4355.013979933767</v>
-      </c>
-      <c r="F43">
-        <v>7567.983765959583</v>
-      </c>
-      <c r="G43">
-        <v>6673.378578951353</v>
-      </c>
-      <c r="H43">
-        <v>2933.40265262258</v>
-      </c>
-      <c r="I43">
-        <v>12591.99304337292</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>887559351.00053</v>
-      </c>
-      <c r="N43">
-        <v>390142552.7988031</v>
-      </c>
-      <c r="O43">
-        <v>1674735074.768598</v>
+        <v>16432657117.36858</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/cases_prev_target_area_sex.xlsx
+++ b/output/Tables/Best practice/cases_prev_target_area_sex.xlsx
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="D2">
-        <v>8253.84642023883</v>
+        <v>18591.25191080866</v>
       </c>
       <c r="E2">
-        <v>7900.64771812378</v>
+        <v>14449.6497278709</v>
       </c>
       <c r="F2">
-        <v>8638.157298867451</v>
+        <v>22794.74894652161</v>
       </c>
       <c r="G2">
-        <v>121395.1226977583</v>
+        <v>283050.5204291867</v>
       </c>
       <c r="H2">
-        <v>109400.9630364136</v>
+        <v>206631.4737818098</v>
       </c>
       <c r="I2">
-        <v>132948.8626566701</v>
+        <v>359159.8735347334</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -475,13 +475,13 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>16145551318.80185</v>
+        <v>37645719217.08183</v>
       </c>
       <c r="N2">
-        <v>14550328083.84301</v>
+        <v>27481986012.98071</v>
       </c>
       <c r="O2">
-        <v>17682198733.33713</v>
+        <v>47768263180.11954</v>
       </c>
     </row>
     <row r="3">
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="D3">
-        <v>7159.110372896416</v>
+        <v>15406.22563314947</v>
       </c>
       <c r="E3">
-        <v>7398.725163138033</v>
+        <v>13033.77691302378</v>
       </c>
       <c r="F3">
-        <v>7018.726506230752</v>
+        <v>17927.12483899367</v>
       </c>
       <c r="G3">
-        <v>97970.7513926964</v>
+        <v>217601.6451690938</v>
       </c>
       <c r="H3">
-        <v>95805.3968277511</v>
+        <v>173161.8588352639</v>
       </c>
       <c r="I3">
-        <v>100772.5730761251</v>
+        <v>263152.1707822582</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>13030109935.22862</v>
+        <v>28941018807.48948</v>
       </c>
       <c r="N3">
-        <v>12742117778.0909</v>
+        <v>23030527225.0901</v>
       </c>
       <c r="O3">
-        <v>13402752219.12464</v>
+        <v>34999238714.04034</v>
       </c>
     </row>
     <row r="4">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="D4">
-        <v>9668.850608764476</v>
+        <v>22809.33461040728</v>
       </c>
       <c r="E4">
-        <v>8705.058033944282</v>
+        <v>16581.89041661676</v>
       </c>
       <c r="F4">
-        <v>10597.12059609972</v>
+        <v>28989.50405386581</v>
       </c>
       <c r="G4">
-        <v>142743.1400039292</v>
+        <v>358968.2377285392</v>
       </c>
       <c r="H4">
-        <v>117152.7275672453</v>
+        <v>238158.4443069333</v>
       </c>
       <c r="I4">
-        <v>166325.0909644189</v>
+        <v>476501.7884561752</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>18984837620.52258</v>
+        <v>47742775617.89571</v>
       </c>
       <c r="N4">
-        <v>15581312766.44362</v>
+        <v>31675073092.82212</v>
       </c>
       <c r="O4">
-        <v>22121237098.26771</v>
+        <v>63374737864.6713</v>
       </c>
     </row>
     <row r="5">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="D5">
-        <v>14843.60734043051</v>
+        <v>33701.6379592509</v>
       </c>
       <c r="E5">
-        <v>14016.41674585004</v>
+        <v>25817.56676691956</v>
       </c>
       <c r="F5">
-        <v>15701.38070724748</v>
+        <v>41662.82007075386</v>
       </c>
       <c r="G5">
-        <v>177126.4044864742</v>
+        <v>417133.133120834</v>
       </c>
       <c r="H5">
-        <v>156721.249581694</v>
+        <v>298993.2315028977</v>
       </c>
       <c r="I5">
-        <v>196505.4098581946</v>
+        <v>534298.2246123115</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>23557811796.70107</v>
+        <v>55478706705.07092</v>
       </c>
       <c r="N5">
-        <v>20843926194.3653</v>
+        <v>39766099789.8854</v>
       </c>
       <c r="O5">
-        <v>26135219511.13988</v>
+        <v>71061663873.43742</v>
       </c>
     </row>
     <row r="6">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="D6">
-        <v>12211.01292613073</v>
+        <v>26510.17121317653</v>
       </c>
       <c r="E6">
-        <v>12427.53263445969</v>
+        <v>22044.09108154453</v>
       </c>
       <c r="F6">
-        <v>12138.26257153001</v>
+        <v>31197.3562211707</v>
       </c>
       <c r="G6">
-        <v>144929.8839420977</v>
+        <v>324263.6579088576</v>
       </c>
       <c r="H6">
-        <v>139878.7812818179</v>
+        <v>254429.025007692</v>
       </c>
       <c r="I6">
-        <v>150677.8160579968</v>
+        <v>395425.0743696365</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>19275674564.29899</v>
+        <v>43127066501.87806</v>
       </c>
       <c r="N6">
-        <v>18603877910.48178</v>
+        <v>33839060326.02303</v>
       </c>
       <c r="O6">
-        <v>20040149535.71357</v>
+        <v>52591534891.16166</v>
       </c>
     </row>
     <row r="7">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="D7">
-        <v>15694.80586331956</v>
+        <v>37823.41754309656</v>
       </c>
       <c r="E7">
-        <v>13691.71794477737</v>
+        <v>26628.98254978137</v>
       </c>
       <c r="F7">
-        <v>17582.77858979543</v>
+        <v>48847.55417786012</v>
       </c>
       <c r="G7">
-        <v>213850.023146182</v>
+        <v>548824.3272958767</v>
       </c>
       <c r="H7">
-        <v>170561.9631321144</v>
+        <v>354601.3133095364</v>
       </c>
       <c r="I7">
-        <v>253486.24003958</v>
+        <v>736879.9950927425</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -740,13 +740,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>28442053078.44221</v>
+        <v>72993635530.35159</v>
       </c>
       <c r="N7">
-        <v>22684741096.57122</v>
+        <v>47161974670.16834</v>
       </c>
       <c r="O7">
-        <v>33713669925.26414</v>
+        <v>98005039347.33475</v>
       </c>
     </row>
     <row r="8">
@@ -766,40 +766,40 @@
         </is>
       </c>
       <c r="D8">
-        <v>4687.844341969944</v>
+        <v>31995.81189377149</v>
       </c>
       <c r="E8">
-        <v>3152.595720089405</v>
+        <v>24430.98325456712</v>
       </c>
       <c r="F8">
-        <v>6435.08892814103</v>
+        <v>39626.57670838545</v>
       </c>
       <c r="G8">
-        <v>5508.569800506694</v>
+        <v>37197.06186638878</v>
       </c>
       <c r="H8">
-        <v>2769.21901644813</v>
+        <v>21356.32585772321</v>
       </c>
       <c r="I8">
-        <v>9430.01576510017</v>
+        <v>57473.86367341727</v>
       </c>
       <c r="J8">
-        <v>261122305.5364092</v>
+        <v>1782230714.106853</v>
       </c>
       <c r="K8">
-        <v>175605886.8004202</v>
+        <v>1360854629.245905</v>
       </c>
       <c r="L8">
-        <v>358447323.4753122</v>
+        <v>2207279575.810488</v>
       </c>
       <c r="M8">
-        <v>732639783.4673903</v>
+        <v>4947209228.229708</v>
       </c>
       <c r="N8">
-        <v>368306129.1876013</v>
+        <v>2840391339.077187</v>
       </c>
       <c r="O8">
-        <v>1254192096.758323</v>
+        <v>7644023868.564497</v>
       </c>
     </row>
     <row r="9">
@@ -819,40 +819,40 @@
         </is>
       </c>
       <c r="D9">
-        <v>3708.71240251773</v>
+        <v>25869.98152961401</v>
       </c>
       <c r="E9">
-        <v>2747.802670320614</v>
+        <v>21466.53994686067</v>
       </c>
       <c r="F9">
-        <v>4837.507922686886</v>
+        <v>30485.38683918802</v>
       </c>
       <c r="G9">
-        <v>4176.843557060938</v>
+        <v>28861.79392298344</v>
       </c>
       <c r="H9">
-        <v>2324.317228707781</v>
+        <v>18107.1948126997</v>
       </c>
       <c r="I9">
-        <v>6806.817169600731</v>
+        <v>42433.31121012401</v>
       </c>
       <c r="J9">
-        <v>206582698.2450425</v>
+        <v>1441009711.162576</v>
       </c>
       <c r="K9">
-        <v>153058104.3421988</v>
+        <v>1195729208.120038</v>
       </c>
       <c r="L9">
-        <v>269458866.3095054</v>
+        <v>1698097017.716452</v>
       </c>
       <c r="M9">
-        <v>555520193.0891048</v>
+        <v>3838618591.756798</v>
       </c>
       <c r="N9">
-        <v>309134191.4181349</v>
+        <v>2408256910.08906</v>
       </c>
       <c r="O9">
-        <v>905306683.5568973</v>
+        <v>5643630390.946493</v>
       </c>
     </row>
     <row r="10">
@@ -872,40 +872,40 @@
         </is>
       </c>
       <c r="D10">
-        <v>5805.284719255748</v>
+        <v>38733.90798980606</v>
       </c>
       <c r="E10">
-        <v>3593.038412385754</v>
+        <v>27445.91923121036</v>
       </c>
       <c r="F10">
-        <v>8251.413091497043</v>
+        <v>49875.66015303666</v>
       </c>
       <c r="G10">
-        <v>7002.395128658082</v>
+        <v>45892.53040880543</v>
       </c>
       <c r="H10">
-        <v>3189.989338027079</v>
+        <v>24031.54512216614</v>
       </c>
       <c r="I10">
-        <v>12421.74868401434</v>
+        <v>74090.44368007933</v>
       </c>
       <c r="J10">
-        <v>323365969.4319832</v>
+        <v>2157556142.848184</v>
       </c>
       <c r="K10">
-        <v>200139425.6467111</v>
+        <v>1528792593.016889</v>
       </c>
       <c r="L10">
-        <v>459620212.0225677</v>
+        <v>2778174021.84444</v>
       </c>
       <c r="M10">
-        <v>931318552.1115249</v>
+        <v>6103706544.371122</v>
       </c>
       <c r="N10">
-        <v>424268581.9576015</v>
+        <v>3196195501.248097</v>
       </c>
       <c r="O10">
-        <v>1652092574.973907</v>
+        <v>9854029009.450552</v>
       </c>
     </row>
     <row r="11">
@@ -925,40 +925,40 @@
         </is>
       </c>
       <c r="D11">
-        <v>7008.923814313164</v>
+        <v>47643.33036970317</v>
       </c>
       <c r="E11">
-        <v>4627.531230201515</v>
+        <v>35797.32880464821</v>
       </c>
       <c r="F11">
-        <v>9706.405273327398</v>
+        <v>59533.05603005933</v>
       </c>
       <c r="G11">
-        <v>6625.168089974998</v>
+        <v>44522.38952795385</v>
       </c>
       <c r="H11">
-        <v>3257.10515275798</v>
+        <v>25059.67818175432</v>
       </c>
       <c r="I11">
-        <v>11453.87714641847</v>
+        <v>69499.22071188496</v>
       </c>
       <c r="J11">
-        <v>390411074.3048729</v>
+        <v>2653828788.253202</v>
       </c>
       <c r="K11">
-        <v>257762744.5846848</v>
+        <v>1993982809.076525</v>
       </c>
       <c r="L11">
-        <v>540666186.5348845</v>
+        <v>3316110286.986366</v>
       </c>
       <c r="M11">
-        <v>881147355.9666748</v>
+        <v>5921477807.217862</v>
       </c>
       <c r="N11">
-        <v>433194985.3168113</v>
+        <v>3332937198.173325</v>
       </c>
       <c r="O11">
-        <v>1523365660.473656</v>
+        <v>9243396354.6807</v>
       </c>
     </row>
     <row r="12">
@@ -978,40 +978,40 @@
         </is>
       </c>
       <c r="D12">
-        <v>5382.043341801748</v>
+        <v>37417.80095152098</v>
       </c>
       <c r="E12">
-        <v>3926.35873289981</v>
+        <v>30645.07607815324</v>
       </c>
       <c r="F12">
-        <v>7082.764038007527</v>
+        <v>44460.77088251285</v>
       </c>
       <c r="G12">
-        <v>4998.730831565939</v>
+        <v>34414.96944734009</v>
       </c>
       <c r="H12">
-        <v>2734.963744078354</v>
+        <v>21279.75672193033</v>
       </c>
       <c r="I12">
-        <v>8219.536670523205</v>
+        <v>51037.13679505853</v>
       </c>
       <c r="J12">
-        <v>299790578.2250413</v>
+        <v>2084246348.601623</v>
       </c>
       <c r="K12">
-        <v>218706034.1399854</v>
+        <v>1706992027.705297</v>
       </c>
       <c r="L12">
-        <v>394524122.4450952</v>
+        <v>2476553859.697726</v>
       </c>
       <c r="M12">
-        <v>664831200.5982699</v>
+        <v>4577190936.496232</v>
       </c>
       <c r="N12">
-        <v>363750177.9624211</v>
+        <v>2830207644.016735</v>
       </c>
       <c r="O12">
-        <v>1093198377.179586</v>
+        <v>6787939193.742785</v>
       </c>
     </row>
     <row r="13">
@@ -1031,40 +1031,40 @@
         </is>
       </c>
       <c r="D13">
-        <v>8155.128332356485</v>
+        <v>53931.23177458264</v>
       </c>
       <c r="E13">
-        <v>4887.340278464571</v>
+        <v>37088.37679744288</v>
       </c>
       <c r="F13">
-        <v>11733.58196480755</v>
+        <v>70446.80924009714</v>
       </c>
       <c r="G13">
-        <v>8752.030267437309</v>
+        <v>56822.68469104824</v>
       </c>
       <c r="H13">
-        <v>3869.556380109978</v>
+        <v>28898.13177822255</v>
       </c>
       <c r="I13">
-        <v>15673.83342815437</v>
+        <v>92901.9002201535</v>
       </c>
       <c r="J13">
-        <v>454256958.3689213</v>
+        <v>3004077472.307816</v>
       </c>
       <c r="K13">
-        <v>272234628.191034</v>
+        <v>2065896764.371169</v>
       </c>
       <c r="L13">
-        <v>653583982.6037109</v>
+        <v>3924028168.291886</v>
       </c>
       <c r="M13">
-        <v>1164020025.569162</v>
+        <v>7557417063.909416</v>
       </c>
       <c r="N13">
-        <v>514650998.5546271</v>
+        <v>3843451526.503599</v>
       </c>
       <c r="O13">
-        <v>2084619845.944531</v>
+        <v>12355952729.28042</v>
       </c>
     </row>
     <row r="14">
@@ -1084,40 +1084,40 @@
         </is>
       </c>
       <c r="D14">
-        <v>4864.771220900318</v>
+        <v>169770.552393671</v>
       </c>
       <c r="E14">
-        <v>1060.289594025195</v>
+        <v>122044.6136709357</v>
       </c>
       <c r="F14">
-        <v>9812.341171753254</v>
+        <v>217132.1466680108</v>
       </c>
       <c r="G14">
-        <v>9118.384506381004</v>
+        <v>315235.1998649222</v>
       </c>
       <c r="H14">
-        <v>1572.32775637972</v>
+        <v>176571.3125472179</v>
       </c>
       <c r="I14">
-        <v>21237.37608941478</v>
+        <v>469145.0937360323</v>
       </c>
       <c r="J14">
-        <v>72032667.46787091</v>
+        <v>2513792569.293095</v>
       </c>
       <c r="K14">
-        <v>15699708.01873104</v>
+        <v>1807114594.625545</v>
       </c>
       <c r="L14">
-        <v>145291335.7301504</v>
+        <v>3215075695.713223</v>
       </c>
       <c r="M14">
-        <v>1212745139.348674</v>
+        <v>41926281582.03465</v>
       </c>
       <c r="N14">
-        <v>209119591.5985027</v>
+        <v>23483984568.77998</v>
       </c>
       <c r="O14">
-        <v>2824571019.892166</v>
+        <v>62396297466.89229</v>
       </c>
     </row>
     <row r="15">
@@ -1137,40 +1137,40 @@
         </is>
       </c>
       <c r="D15">
-        <v>3559.942352286718</v>
+        <v>131292.7759875948</v>
       </c>
       <c r="E15">
-        <v>775.898733992386</v>
+        <v>102459.9090399153</v>
       </c>
       <c r="F15">
-        <v>7180.475160339917</v>
+        <v>160608.9543510892</v>
       </c>
       <c r="G15">
-        <v>6708.180819770454</v>
+        <v>243943.7003659807</v>
       </c>
       <c r="H15">
-        <v>1156.724515220647</v>
+        <v>147390.6673706159</v>
       </c>
       <c r="I15">
-        <v>15623.83762667257</v>
+        <v>348852.1172920821</v>
       </c>
       <c r="J15">
-        <v>52712066.41030943</v>
+        <v>1944052134.048312</v>
       </c>
       <c r="K15">
-        <v>11488732.55422525</v>
+        <v>1517123873.154023</v>
       </c>
       <c r="L15">
-        <v>106321295.6991528</v>
+        <v>2378136787.076574</v>
       </c>
       <c r="M15">
-        <v>892188049.0294704</v>
+        <v>32444512148.67543</v>
       </c>
       <c r="N15">
-        <v>153844360.5243461</v>
+        <v>19602958760.29192</v>
       </c>
       <c r="O15">
-        <v>2077970404.347451</v>
+        <v>46397331599.84692</v>
       </c>
     </row>
     <row r="16">
@@ -1190,40 +1190,40 @@
         </is>
       </c>
       <c r="D16">
-        <v>7192.012576144401</v>
+        <v>227943.2209115641</v>
       </c>
       <c r="E16">
-        <v>1386.536862302079</v>
+        <v>147920.0567822066</v>
       </c>
       <c r="F16">
-        <v>14562.37346730163</v>
+        <v>305383.6967215876</v>
       </c>
       <c r="G16">
-        <v>14438.30653172097</v>
+        <v>449271.8630600378</v>
       </c>
       <c r="H16">
-        <v>2114.134885455231</v>
+        <v>226038.8051748526</v>
       </c>
       <c r="I16">
-        <v>33797.27124008795</v>
+        <v>700771.7540641753</v>
       </c>
       <c r="J16">
-        <v>106492130.2149702</v>
+        <v>3375155272.037534</v>
       </c>
       <c r="K16">
-        <v>20530451.3201069</v>
+        <v>2190252280.774139</v>
       </c>
       <c r="L16">
-        <v>215625063.9303355</v>
+        <v>4521816397.356509</v>
       </c>
       <c r="M16">
-        <v>1920294768.71889</v>
+        <v>59753157786.98503</v>
       </c>
       <c r="N16">
-        <v>281179939.7655457</v>
+        <v>30063161088.2554</v>
       </c>
       <c r="O16">
-        <v>4495037074.931697</v>
+        <v>93202643290.53531</v>
       </c>
     </row>
     <row r="17">
@@ -1243,40 +1243,40 @@
         </is>
       </c>
       <c r="D17">
-        <v>2943.198685913449</v>
+        <v>104066.8678830935</v>
       </c>
       <c r="E17">
-        <v>641.4778410165663</v>
+        <v>76369.71418045239</v>
       </c>
       <c r="F17">
-        <v>5936.490809344574</v>
+        <v>131688.0569680401</v>
       </c>
       <c r="G17">
-        <v>3370.588964715729</v>
+        <v>116808.247203599</v>
       </c>
       <c r="H17">
-        <v>581.2071843275567</v>
+        <v>65670.12165360276</v>
       </c>
       <c r="I17">
-        <v>7850.345139142364</v>
+        <v>173518.3672674076</v>
       </c>
       <c r="J17">
-        <v>43579942.94232056</v>
+        <v>1540918112.744962</v>
       </c>
       <c r="K17">
-        <v>9498362.391932283</v>
+        <v>1130806357.869954</v>
       </c>
       <c r="L17">
-        <v>87901619.41396514</v>
+        <v>1949905059.525775</v>
       </c>
       <c r="M17">
-        <v>448288332.307192</v>
+        <v>15535496878.07866</v>
       </c>
       <c r="N17">
-        <v>77300555.51556504</v>
+        <v>8734126179.929167</v>
       </c>
       <c r="O17">
-        <v>1044095903.505934</v>
+        <v>23077942846.56521</v>
       </c>
     </row>
     <row r="18">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D18">
-        <v>2165.33972017152</v>
+        <v>81232.67026210747</v>
       </c>
       <c r="E18">
-        <v>471.941447721844</v>
+        <v>65012.36254092129</v>
       </c>
       <c r="F18">
-        <v>4367.533666493687</v>
+        <v>97901.20683656198</v>
       </c>
       <c r="G18">
-        <v>2461.075219908059</v>
+        <v>90303.27490640213</v>
       </c>
       <c r="H18">
-        <v>424.3752691161218</v>
+        <v>55291.92101547005</v>
       </c>
       <c r="I18">
-        <v>5732.021937981513</v>
+        <v>128171.4719572462</v>
       </c>
       <c r="J18">
-        <v>32062185.23657968</v>
+        <v>1202812148.571023</v>
       </c>
       <c r="K18">
-        <v>6988037.01641736</v>
+        <v>962638052.1434187</v>
       </c>
       <c r="L18">
-        <v>64670070.99977201</v>
+        <v>1449623169.62895</v>
       </c>
       <c r="M18">
-        <v>327323004.2477719</v>
+        <v>12010335562.55148</v>
       </c>
       <c r="N18">
-        <v>56441910.79244421</v>
+        <v>7353825495.057516</v>
       </c>
       <c r="O18">
-        <v>762358917.7515413</v>
+        <v>17046805770.31374</v>
       </c>
     </row>
     <row r="19">
@@ -1349,40 +1349,40 @@
         </is>
       </c>
       <c r="D19">
-        <v>3977.939897297059</v>
+        <v>128943.5349918105</v>
       </c>
       <c r="E19">
-        <v>802.3522507055084</v>
+        <v>85670.41856522919</v>
       </c>
       <c r="F19">
-        <v>8043.567431528649</v>
+        <v>171048.5251466759</v>
       </c>
       <c r="G19">
-        <v>5240.304728400624</v>
+        <v>164271.5532222023</v>
       </c>
       <c r="H19">
-        <v>791.3809991924962</v>
+        <v>83044.29274070406</v>
       </c>
       <c r="I19">
-        <v>12255.6781953113</v>
+        <v>255796.770807725</v>
       </c>
       <c r="J19">
-        <v>58901356.0592775</v>
+        <v>1909266922.623736</v>
       </c>
       <c r="K19">
-        <v>11880429.77619646</v>
+        <v>1268521887.695353</v>
       </c>
       <c r="L19">
-        <v>119101102.9586445</v>
+        <v>2532715511.846808</v>
       </c>
       <c r="M19">
-        <v>696960528.877283</v>
+        <v>21848116578.55291</v>
       </c>
       <c r="N19">
-        <v>105253672.892602</v>
+        <v>11044890934.51364</v>
       </c>
       <c r="O19">
-        <v>1630005199.976403</v>
+        <v>34020970517.42742</v>
       </c>
     </row>
     <row r="20">
@@ -1402,40 +1402,40 @@
         </is>
       </c>
       <c r="D20">
-        <v>758.7457610219977</v>
+        <v>12001.57780324606</v>
       </c>
       <c r="E20">
-        <v>-60.16649273703359</v>
+        <v>8598.512028267034</v>
       </c>
       <c r="F20">
-        <v>1529.149155900641</v>
+        <v>15376.26217061853</v>
       </c>
       <c r="G20">
-        <v>1632.108725067148</v>
+        <v>25654.12930279909</v>
       </c>
       <c r="H20">
-        <v>-96.31436630534563</v>
+        <v>13541.58672953716</v>
       </c>
       <c r="I20">
-        <v>4176.140162739625</v>
+        <v>41940.14215481259</v>
       </c>
       <c r="J20">
-        <v>57058439.97461542</v>
+        <v>902530652.3819052</v>
       </c>
       <c r="K20">
-        <v>-4524580.420317656</v>
+        <v>646616703.0377098</v>
       </c>
       <c r="L20">
-        <v>114993545.6728838</v>
+        <v>1156310291.492683</v>
       </c>
       <c r="M20">
-        <v>217070460.4339306</v>
+        <v>3411999197.27228</v>
       </c>
       <c r="N20">
-        <v>-12809810.71861097</v>
+        <v>1801031035.028442</v>
       </c>
       <c r="O20">
-        <v>555426641.6443702</v>
+        <v>5578038906.590075</v>
       </c>
     </row>
     <row r="21">
@@ -1455,40 +1455,40 @@
         </is>
       </c>
       <c r="D21">
-        <v>543.8805687008911</v>
+        <v>9144.992550091014</v>
       </c>
       <c r="E21">
-        <v>-43.12826241359065</v>
+        <v>7173.546044569091</v>
       </c>
       <c r="F21">
-        <v>1096.117507687289</v>
+        <v>11153.69399123778</v>
       </c>
       <c r="G21">
-        <v>1175.397060655109</v>
+        <v>19563.56538537014</v>
       </c>
       <c r="H21">
-        <v>-69.36279508554547</v>
+        <v>11249.59759847645</v>
       </c>
       <c r="I21">
-        <v>3007.534238851616</v>
+        <v>30558.32447060974</v>
       </c>
       <c r="J21">
-        <v>40900362.6468757</v>
+        <v>687712584.7593933</v>
       </c>
       <c r="K21">
-        <v>-3243288.46176442</v>
+        <v>539457836.097638</v>
       </c>
       <c r="L21">
-        <v>82429132.69559166</v>
+        <v>838768941.8350779</v>
       </c>
       <c r="M21">
-        <v>156327809.0671294</v>
+        <v>2601954196.254229</v>
       </c>
       <c r="N21">
-        <v>-9225251.746377548</v>
+        <v>1496196480.597368</v>
       </c>
       <c r="O21">
-        <v>400002053.7672649</v>
+        <v>4064257154.591096</v>
       </c>
     </row>
     <row r="22">
@@ -1508,40 +1508,40 @@
         </is>
       </c>
       <c r="D22">
-        <v>1067.675666851944</v>
+        <v>15414.27520728188</v>
       </c>
       <c r="E22">
-        <v>-80.04343457346833</v>
+        <v>10000.17057587619</v>
       </c>
       <c r="F22">
-        <v>2137.130433342855</v>
+        <v>20661.35507800402</v>
       </c>
       <c r="G22">
-        <v>2455.370387430866</v>
+        <v>34896.06773771309</v>
       </c>
       <c r="H22">
-        <v>-133.9002434626026</v>
+        <v>16609.19443459751</v>
       </c>
       <c r="I22">
-        <v>6223.267918041822</v>
+        <v>59726.2971561318</v>
       </c>
       <c r="J22">
-        <v>80290277.82293293</v>
+        <v>1159168909.862805</v>
       </c>
       <c r="K22">
-        <v>-6019346.323359375</v>
+        <v>752022827.4764686</v>
       </c>
       <c r="L22">
-        <v>160714345.7178162</v>
+        <v>1553754563.220986</v>
       </c>
       <c r="M22">
-        <v>326564261.5283052</v>
+        <v>4641177009.11584</v>
       </c>
       <c r="N22">
-        <v>-17808732.38052614</v>
+        <v>2209022859.801468</v>
       </c>
       <c r="O22">
-        <v>827694633.0995623</v>
+        <v>7943597521.765529</v>
       </c>
     </row>
     <row r="23">
@@ -1561,40 +1561,40 @@
         </is>
       </c>
       <c r="D23">
-        <v>1082.033409135065</v>
+        <v>17042.33417614646</v>
       </c>
       <c r="E23">
-        <v>-85.80233142161192</v>
+        <v>12127.5498518898</v>
       </c>
       <c r="F23">
-        <v>2180.691556031257</v>
+        <v>21908.97362707969</v>
       </c>
       <c r="G23">
-        <v>2038.868515051613</v>
+        <v>31943.4777915511</v>
       </c>
       <c r="H23">
-        <v>-120.318166302945</v>
+        <v>16774.59175345992</v>
       </c>
       <c r="I23">
-        <v>5216.932279987687</v>
+        <v>52356.1331457413</v>
       </c>
       <c r="J23">
-        <v>81369994.40036626</v>
+        <v>1281600572.380395</v>
       </c>
       <c r="K23">
-        <v>-6452421.125236639</v>
+        <v>912003876.4119701</v>
       </c>
       <c r="L23">
-        <v>163990185.7051065</v>
+        <v>1647576725.730019</v>
       </c>
       <c r="M23">
-        <v>271169512.5018645</v>
+        <v>4248482546.276297</v>
       </c>
       <c r="N23">
-        <v>-16002316.11829169</v>
+        <v>2231020703.21017</v>
       </c>
       <c r="O23">
-        <v>693851993.2383624</v>
+        <v>6963365708.383593</v>
       </c>
     </row>
     <row r="24">
@@ -1614,40 +1614,40 @@
         </is>
       </c>
       <c r="D24">
-        <v>786.6290410376989</v>
+        <v>13142.45842375526</v>
       </c>
       <c r="E24">
-        <v>-62.37756164935282</v>
+        <v>10212.88521095764</v>
       </c>
       <c r="F24">
-        <v>1585.34412434741</v>
+        <v>16116.61928177844</v>
       </c>
       <c r="G24">
-        <v>1494.340577476141</v>
+        <v>24681.34054997219</v>
       </c>
       <c r="H24">
-        <v>-88.18436146651824</v>
+        <v>14029.85315328237</v>
       </c>
       <c r="I24">
-        <v>3823.627437659141</v>
+        <v>38803.86331560556</v>
       </c>
       <c r="J24">
-        <v>59155290.51507618</v>
+        <v>988326015.9248221</v>
       </c>
       <c r="K24">
-        <v>-4690855.013592984</v>
+        <v>768019180.7492238</v>
       </c>
       <c r="L24">
-        <v>119219463.4950496</v>
+        <v>1211985886.609024</v>
       </c>
       <c r="M24">
-        <v>198747296.8043267</v>
+        <v>3282618293.146302</v>
       </c>
       <c r="N24">
-        <v>-11728520.07504693</v>
+        <v>1865970469.386555</v>
       </c>
       <c r="O24">
-        <v>508542449.2086657</v>
+        <v>5160913820.975539</v>
       </c>
     </row>
     <row r="25">
@@ -1667,40 +1667,40 @@
         </is>
       </c>
       <c r="D25">
-        <v>1644.116453384767</v>
+        <v>23386.56118191829</v>
       </c>
       <c r="E25">
-        <v>-120.8564014989858</v>
+        <v>14963.5982872497</v>
       </c>
       <c r="F25">
-        <v>3283.36722572006</v>
+        <v>31522.92227269608</v>
       </c>
       <c r="G25">
-        <v>3398.746929158277</v>
+        <v>47648.62863145903</v>
       </c>
       <c r="H25">
-        <v>-181.0793428443642</v>
+        <v>22428.28248835712</v>
       </c>
       <c r="I25">
-        <v>8591.265653892089</v>
+        <v>81901.37533864009</v>
       </c>
       <c r="J25">
-        <v>123639201.4109879</v>
+        <v>1758692787.441447</v>
       </c>
       <c r="K25">
-        <v>-9088522.249125211</v>
+        <v>1125277554.799469</v>
       </c>
       <c r="L25">
-        <v>246912498.7413736</v>
+        <v>2370555277.829007</v>
       </c>
       <c r="M25">
-        <v>452033341.5780509</v>
+        <v>6337267607.984052</v>
       </c>
       <c r="N25">
-        <v>-24083552.59830045</v>
+        <v>2982961570.951498</v>
       </c>
       <c r="O25">
-        <v>1142638331.967648</v>
+        <v>10892882920.03913</v>
       </c>
     </row>
     <row r="26">
@@ -1720,40 +1720,40 @@
         </is>
       </c>
       <c r="D26">
-        <v>1751.429393137576</v>
+        <v>8026.121027393206</v>
       </c>
       <c r="E26">
-        <v>1452.226991656893</v>
+        <v>6406.514507456995</v>
       </c>
       <c r="F26">
-        <v>2039.358846460138</v>
+        <v>9688.270249344954</v>
       </c>
       <c r="G26">
-        <v>3916.057058909889</v>
+        <v>17634.33570111627</v>
       </c>
       <c r="H26">
-        <v>2484.655924856676</v>
+        <v>10747.60225702336</v>
       </c>
       <c r="I26">
-        <v>5345.155598953805</v>
+        <v>24937.9884306703</v>
       </c>
       <c r="J26">
-        <v>29492319.55104359</v>
+        <v>135151851.9802743</v>
       </c>
       <c r="K26">
-        <v>24454050.31251043</v>
+        <v>107879297.7910685</v>
       </c>
       <c r="L26">
-        <v>34340763.61554222</v>
+        <v>163140782.7287201</v>
       </c>
       <c r="M26">
-        <v>520835588.8350153</v>
+        <v>2345366648.248465</v>
       </c>
       <c r="N26">
-        <v>330459238.0059379</v>
+        <v>1429431100.184107</v>
       </c>
       <c r="O26">
-        <v>710905694.660856</v>
+        <v>3316752461.27915</v>
       </c>
     </row>
     <row r="27">
@@ -1773,40 +1773,40 @@
         </is>
       </c>
       <c r="D27">
-        <v>1443.781464982335</v>
+        <v>6798.874274353729</v>
       </c>
       <c r="E27">
-        <v>1290.110710163457</v>
+        <v>5846.337503720341</v>
       </c>
       <c r="F27">
-        <v>1597.570145249</v>
+        <v>7825.508907439428</v>
       </c>
       <c r="G27">
-        <v>3062.181862612254</v>
+        <v>14185.40786712287</v>
       </c>
       <c r="H27">
-        <v>2095.516575980358</v>
+        <v>9348.821366432456</v>
       </c>
       <c r="I27">
-        <v>3985.027869796784</v>
+        <v>19154.85421257596</v>
       </c>
       <c r="J27">
-        <v>24311836.08883753</v>
+        <v>114486243.9058423</v>
       </c>
       <c r="K27">
-        <v>21724174.24844243</v>
+        <v>98446477.22514705</v>
       </c>
       <c r="L27">
-        <v>26901483.67584785</v>
+        <v>131773744.4923735</v>
       </c>
       <c r="M27">
-        <v>407270187.7274298</v>
+        <v>1886659246.327342</v>
       </c>
       <c r="N27">
-        <v>278703704.6053876</v>
+        <v>1243393241.735517</v>
       </c>
       <c r="O27">
-        <v>530008706.6829723</v>
+        <v>2547595610.272603</v>
       </c>
     </row>
     <row r="28">
@@ -1826,40 +1826,40 @@
         </is>
       </c>
       <c r="D28">
-        <v>2166.271502732026</v>
+        <v>9708.691251087888</v>
       </c>
       <c r="E28">
-        <v>1698.570538874215</v>
+        <v>7305.385324150751</v>
       </c>
       <c r="F28">
-        <v>2609.96162781205</v>
+        <v>12120.29674041241</v>
       </c>
       <c r="G28">
-        <v>4879.810044502176</v>
+        <v>21303.53834289802</v>
       </c>
       <c r="H28">
-        <v>2882.091888233809</v>
+        <v>11981.53136899531</v>
       </c>
       <c r="I28">
-        <v>6932.6862861466</v>
+        <v>31402.1760651783</v>
       </c>
       <c r="J28">
-        <v>36477845.8345046</v>
+        <v>163484651.9770693</v>
       </c>
       <c r="K28">
-        <v>28602229.30410286</v>
+        <v>123015383.4733741</v>
       </c>
       <c r="L28">
-        <v>43949143.85072712</v>
+        <v>204093676.8118037</v>
       </c>
       <c r="M28">
-        <v>649014735.9187895</v>
+        <v>2833370599.605436</v>
       </c>
       <c r="N28">
-        <v>383318221.1350965</v>
+        <v>1593543672.076377</v>
       </c>
       <c r="O28">
-        <v>922047276.0574977</v>
+        <v>4176489416.668715</v>
       </c>
     </row>
     <row r="29">
@@ -1879,40 +1879,40 @@
         </is>
       </c>
       <c r="D29">
-        <v>1404.784553633325</v>
+        <v>6420.828510079357</v>
       </c>
       <c r="E29">
-        <v>1156.777763122008</v>
+        <v>5088.820735210512</v>
       </c>
       <c r="F29">
-        <v>1642.93046329017</v>
+        <v>7783.48155855021</v>
       </c>
       <c r="G29">
-        <v>1991.198639260032</v>
+        <v>8870.106721472464</v>
       </c>
       <c r="H29">
-        <v>1226.755749223694</v>
+        <v>5237.142733878604</v>
       </c>
       <c r="I29">
-        <v>2764.540690032691</v>
+        <v>12761.28467651994</v>
       </c>
       <c r="J29">
-        <v>23655167.09863161</v>
+        <v>108120331.2812261</v>
       </c>
       <c r="K29">
-        <v>19478980.75321149</v>
+        <v>85690652.36020984</v>
       </c>
       <c r="L29">
-        <v>27665306.07134325</v>
+        <v>131066045.9644276</v>
       </c>
       <c r="M29">
-        <v>264829419.0215843</v>
+        <v>1179724193.955838</v>
       </c>
       <c r="N29">
-        <v>163158514.6467513</v>
+        <v>696539983.6058544</v>
       </c>
       <c r="O29">
-        <v>367683911.7743478</v>
+        <v>1697250861.977152</v>
       </c>
     </row>
     <row r="30">
@@ -1932,40 +1932,40 @@
         </is>
       </c>
       <c r="D30">
-        <v>1095.455908257531</v>
+        <v>5144.133951288902</v>
       </c>
       <c r="E30">
-        <v>971.2334641020432</v>
+        <v>4389.994850501884</v>
       </c>
       <c r="F30">
-        <v>1218.999635328685</v>
+        <v>5951.350724089593</v>
       </c>
       <c r="G30">
-        <v>1545.029911519845</v>
+        <v>7106.050056859836</v>
       </c>
       <c r="H30">
-        <v>1036.118178793872</v>
+        <v>4588.711446578765</v>
       </c>
       <c r="I30">
-        <v>2037.693206988772</v>
+        <v>9717.544294399035</v>
       </c>
       <c r="J30">
-        <v>18446382.03914857</v>
+        <v>86622071.60575408</v>
       </c>
       <c r="K30">
-        <v>16354600.30201432</v>
+        <v>73923123.28760134</v>
       </c>
       <c r="L30">
-        <v>20526734.85929978</v>
+        <v>100214794.842945</v>
       </c>
       <c r="M30">
-        <v>205488978.2321393</v>
+        <v>945104657.5623583</v>
       </c>
       <c r="N30">
-        <v>137803717.7795849</v>
+        <v>610298622.3949758</v>
       </c>
       <c r="O30">
-        <v>271013196.5295067</v>
+        <v>1292433391.155071</v>
       </c>
     </row>
     <row r="31">
@@ -1985,40 +1985,40 @@
         </is>
       </c>
       <c r="D31">
-        <v>1482.203267110881</v>
+        <v>6604.830275682478</v>
       </c>
       <c r="E31">
-        <v>1146.621587111518</v>
+        <v>4896.83426674684</v>
       </c>
       <c r="F31">
-        <v>1799.728459276041</v>
+        <v>8311.013504243892</v>
       </c>
       <c r="G31">
-        <v>2366.292157278386</v>
+        <v>10163.12264576558</v>
       </c>
       <c r="H31">
-        <v>1347.385759074039</v>
+        <v>5471.703576212788</v>
       </c>
       <c r="I31">
-        <v>3425.472626599474</v>
+        <v>15290.00976793471</v>
       </c>
       <c r="J31">
-        <v>24958820.8148801</v>
+        <v>111218737.0122174</v>
       </c>
       <c r="K31">
-        <v>19307960.90537084</v>
+        <v>82457792.21774977</v>
       </c>
       <c r="L31">
-        <v>30305627.52574926</v>
+        <v>139949156.3979629</v>
       </c>
       <c r="M31">
-        <v>314716856.9180253</v>
+        <v>1351695311.886822</v>
       </c>
       <c r="N31">
-        <v>179202305.9568473</v>
+        <v>727736575.6363008</v>
       </c>
       <c r="O31">
-        <v>455587859.33773</v>
+        <v>2033571299.135317</v>
       </c>
     </row>
     <row r="32">
@@ -2038,22 +2038,22 @@
         </is>
       </c>
       <c r="D32">
-        <v>27229.71362371212</v>
+        <v>252193.3306136017</v>
       </c>
       <c r="E32">
-        <v>19342.0557325939</v>
+        <v>181260.953718121</v>
       </c>
       <c r="F32">
-        <v>33626.07852962624</v>
+        <v>322580.5414878041</v>
       </c>
       <c r="G32">
-        <v>84301.80071209511</v>
+        <v>773067.2639856773</v>
       </c>
       <c r="H32">
-        <v>37042.89974154739</v>
+        <v>338199.810105756</v>
       </c>
       <c r="I32">
-        <v>159079.0458373938</v>
+        <v>1523335.174134585</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -2065,13 +2065,13 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>11212139494.70865</v>
+        <v>102817946110.0951</v>
       </c>
       <c r="N32">
-        <v>4926705665.625802</v>
+        <v>44980574744.06554</v>
       </c>
       <c r="O32">
-        <v>21157513096.37338</v>
+        <v>202603578159.8998</v>
       </c>
     </row>
     <row r="33">
@@ -2091,22 +2091,22 @@
         </is>
       </c>
       <c r="D33">
-        <v>20097.78915929206</v>
+        <v>196195.5202200281</v>
       </c>
       <c r="E33">
-        <v>14276.04283294534</v>
+        <v>152496.2703859727</v>
       </c>
       <c r="F33">
-        <v>24818.83746121083</v>
+        <v>240559.2843178337</v>
       </c>
       <c r="G33">
-        <v>62224.14202283687</v>
+        <v>599134.7767456835</v>
       </c>
       <c r="H33">
-        <v>27341.79620109869</v>
+        <v>281969.327395252</v>
       </c>
       <c r="I33">
-        <v>117418.0985154587</v>
+        <v>1136228.173431341</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -2118,13 +2118,13 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>8275810889.037303</v>
+        <v>79684925307.1759</v>
       </c>
       <c r="N33">
-        <v>3636458894.746126</v>
+        <v>37501920543.56852</v>
       </c>
       <c r="O33">
-        <v>15616607102.556</v>
+        <v>151118347066.3683</v>
       </c>
     </row>
     <row r="34">
@@ -2144,22 +2144,22 @@
         </is>
       </c>
       <c r="D34">
-        <v>41432.09422520552</v>
+        <v>351464.418906644</v>
       </c>
       <c r="E34">
-        <v>29598.55131878856</v>
+        <v>228292.2611925646</v>
       </c>
       <c r="F34">
-        <v>51113.88206723896</v>
+        <v>470616.4419439731</v>
       </c>
       <c r="G34">
-        <v>137230.2558237958</v>
+        <v>1148338.364205588</v>
       </c>
       <c r="H34">
-        <v>60723.0700272856</v>
+        <v>453092.3336430843</v>
       </c>
       <c r="I34">
-        <v>258640.5018472947</v>
+        <v>2367245.51223302</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -2171,13 +2171,13 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>18251624024.56485</v>
+        <v>152729002439.3432</v>
       </c>
       <c r="N34">
-        <v>8076168313.628985</v>
+        <v>60261280374.53021</v>
       </c>
       <c r="O34">
-        <v>34399186745.69019</v>
+        <v>314843653126.9916</v>
       </c>
     </row>
     <row r="35">
@@ -2197,22 +2197,22 @@
         </is>
       </c>
       <c r="D35">
-        <v>14364.40871190271</v>
+        <v>132795.8356339544</v>
       </c>
       <c r="E35">
-        <v>10203.45633122762</v>
+        <v>95161.05688287194</v>
       </c>
       <c r="F35">
-        <v>17738.66380135072</v>
+        <v>170116.8111303829</v>
       </c>
       <c r="G35">
-        <v>37836.07740130918</v>
+        <v>346336.7271694562</v>
       </c>
       <c r="H35">
-        <v>16625.48142449141</v>
+        <v>151061.120557176</v>
       </c>
       <c r="I35">
-        <v>71397.37277719221</v>
+        <v>683473.7475731806</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -2224,13 +2224,13 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>5032198294.374121</v>
+        <v>46062784713.53767</v>
       </c>
       <c r="N35">
-        <v>2211189029.457358</v>
+        <v>20091129034.10441</v>
       </c>
       <c r="O35">
-        <v>9495850579.366564</v>
+        <v>90902008427.23302</v>
       </c>
     </row>
     <row r="36">
@@ -2250,22 +2250,22 @@
         </is>
       </c>
       <c r="D36">
-        <v>10566.24417500289</v>
+        <v>102907.1277728172</v>
       </c>
       <c r="E36">
-        <v>7505.509846388188</v>
+        <v>79693.66572594752</v>
       </c>
       <c r="F36">
-        <v>13048.29574419216</v>
+        <v>126442.3949060549</v>
       </c>
       <c r="G36">
-        <v>27657.20615718402</v>
+        <v>265547.3751118976</v>
       </c>
       <c r="H36">
-        <v>12152.80226706807</v>
+        <v>124421.997599664</v>
       </c>
       <c r="I36">
-        <v>52189.65584185514</v>
+        <v>504834.0668980748</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -2277,13 +2277,13 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <v>3678408418.905475</v>
+        <v>35317800889.88238</v>
       </c>
       <c r="N36">
-        <v>1616322701.520054</v>
+        <v>16548125680.75531</v>
       </c>
       <c r="O36">
-        <v>6941224226.966733</v>
+        <v>67142930897.44395</v>
       </c>
     </row>
     <row r="37">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="D37">
-        <v>22668.93349040181</v>
+        <v>190995.8006273227</v>
       </c>
       <c r="E37">
-        <v>16203.53610441969</v>
+        <v>122971.3532998864</v>
       </c>
       <c r="F37">
-        <v>27963.41374996311</v>
+        <v>256682.9770891214</v>
       </c>
       <c r="G37">
-        <v>65562.36040230785</v>
+        <v>546162.9662043487</v>
       </c>
       <c r="H37">
-        <v>29027.91250159551</v>
+        <v>214381.5517565983</v>
       </c>
       <c r="I37">
-        <v>123553.8129125457</v>
+        <v>1128169.429782592</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -2330,13 +2330,13 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>8719793933.506945</v>
+        <v>72639674505.17838</v>
       </c>
       <c r="N37">
-        <v>3860712362.712203</v>
+        <v>28512746383.62757</v>
       </c>
       <c r="O37">
-        <v>16432657117.36858</v>
+        <v>150046534161.0848</v>
       </c>
     </row>
   </sheetData>
